--- a/DDL.xlsx
+++ b/DDL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\C# Training\Submission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF36D906-7F3F-4417-A212-66ECC1988200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E494F5-0214-4804-B2DA-6C28EC4FA7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{75F2628D-93A2-47B8-ACCD-44203D0678B4}"/>
   </bookViews>
@@ -35,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="80">
   <si>
     <t>-- BANK AND BRANCH</t>
   </si>
@@ -180,9 +158,6 @@
     <t xml:space="preserve">    PRIMARY KEY (UserID, RoleID)</t>
   </si>
   <si>
-    <t>-- ======================</t>
-  </si>
-  <si>
     <t>CREATE TABLE Employee (</t>
   </si>
   <si>
@@ -249,9 +224,6 @@
     <t xml:space="preserve">    CreatedDate DATETIME DEFAULT GETDATE()</t>
   </si>
   <si>
-    <t>-- POWER OF ATTORNEY</t>
-  </si>
-  <si>
     <t>CREATE TABLE PowerOfAttorney (</t>
   </si>
   <si>
@@ -301,6 +273,9 @@
   </si>
   <si>
     <t xml:space="preserve">    Remarks NVARCHAR(250)</t>
+  </si>
+  <si>
+    <t>PasswordHash NVARCHAR(255) NOT NULL,</t>
   </si>
 </sst>
 </file>
@@ -672,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82923037-64B1-463C-AFCB-92195C561CFD}">
-  <dimension ref="A1:A141"/>
+  <dimension ref="A1:A142"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -765,12 +740,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="e" cm="1">
-        <f t="array" ref="A22">-- ROLES &amp; PERMISSIONS</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
@@ -846,12 +815,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="e" cm="1">
-        <f t="array" ref="A42">-- USERS</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>27</v>
@@ -879,405 +842,371 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>37</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="e" cm="1">
-        <f t="array" ref="A64">-- EMPLOYEES</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>46</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="e" cm="1">
-        <f t="array" ref="A91">-- ACCOUNTS</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>53</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A118" t="e" cm="1">
-        <f t="array" ref="A118">-- ACCOUNT OPERATORS (LIMITED ACCESS)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>70</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A130" t="e" cm="1">
-        <f t="array" ref="A130">-- TRANSACTIONS</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>74</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>7</v>
       </c>
     </row>
